--- a/jpcore-r4b/develop/StructureDefinition-jp-allergyintolerance.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-allergyintolerance.xlsx
@@ -69,7 +69,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) (http://jpfhir.jp, office@hlfhir.jp)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/jpcore-r4b/develop/StructureDefinition-jp-allergyintolerance.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-allergyintolerance.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-dev</t>
+    <t>2.0.0-dev-temp</t>
   </si>
   <si>
     <t>Name</t>
@@ -90,7 +90,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>FHIR Version</t>
@@ -369,7 +369,7 @@
     <t>IETF language tag</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.3.0</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -963,7 +963,7 @@
     <t>Codes defining the type of the substance (including pharmaceutical products).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/substance-code</t>
+    <t>http://hl7.org/fhir/ValueSet/substance-code|4.3.0</t>
   </si>
   <si>
     <t>outBoundRelationship[typeCode=SAS].target[classCode=SBADM, code &lt;= ExposureCode].participation[typeCode=CSM].role[classCode=ADMM].player[classCode=MAT, determinerCode=KIND, code &lt;= ExposureAgentEntityType]</t>
@@ -989,7 +989,7 @@
     <t>Clinical symptoms and/or signs that are observed or associated with an Adverse Reaction Event.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/clinical-findings</t>
+    <t>http://hl7.org/fhir/ValueSet/clinical-findings|4.3.0</t>
   </si>
   <si>
     <t>AL1-5</t>
@@ -1063,7 +1063,7 @@
     <t>A coded concept describing the route or physiological path of administration of a therapeutic agent into or onto the body of a subject.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/route-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/route-codes|4.3.0</t>
   </si>
   <si>
     <t>outBoundRelationship[typeCode=SAS].target[classCode=SBADM, code &lt;= ExposureCode].routeCode</t>
@@ -1386,17 +1386,17 @@
   <dimension ref="A1:AM36"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="43.109375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="43.109375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="36.9609375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="36.9609375" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="185.2109375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="158.78515625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1405,25 +1405,25 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="124.42578125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="59.046875" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="40.39453125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="106.67578125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="50.62109375" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="34.6328125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="40.265625" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="34.51953125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/jpcore-r4b/develop/StructureDefinition-jp-allergyintolerance.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-allergyintolerance.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-dev-temp</t>
+    <t>2.0.0-dev</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4b/develop/StructureDefinition-jp-allergyintolerance.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-allergyintolerance.xlsx
@@ -270,11 +270,11 @@
 このリソースは患者のアレルギー不耐症を表現する。具体的には、特定の物質または物質群への暴露によって生じる有害反応の傾向や、潜在的なリスクを表現する。</t>
   </si>
   <si>
-    <t>Substances include, but are not limited to: a therapeutic substance administered correctly at an appropriate dosage for the individual; food; material derived from plants or animals; or venom from insect stings.</t>
-  </si>
-  <si>
-    <t>ait-1:AllergyIntolerance.clinicalStatus SHALL be present if verificationStatus is not entered-in-error. {(verificationStatus.exists() and verificationStatus.coding.where(system='http://terminology.hl7.org/CodeSystem/allergyintolerance-verification' and code='entered-in-error').exists().not()) implies clinicalStatus.exists()}
-ait-2:AllergyIntolerance.clinicalStatus SHALL NOT be present if verification Status is entered-in-error {(verificationStatus.coding.where(system='http://terminology.hl7.org/CodeSystem/allergyintolerance-verification' and code='entered-in-error').exists()) implies clinicalStatus.exists().not()}dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where(((id.exists() and ('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url)))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(uri) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
+    <t>物質には、個人に適切な投与量で正しく投与される治療物質が含まれますが、これらに限定されません。食物;植物または動物に由来する材料。または昆虫の刺し傷からの毒。 / Substances include, but are not limited to: a therapeutic substance administered correctly at an appropriate dosage for the individual; food; material derived from plants or animals; or venom from insect stings.</t>
+  </si>
+  <si>
+    <t>ait-1:AllergyIntolerance.verificationStatusに'entered-in-error'が入力されていない場合には、AllergyIntolerance.ClinicalStatusは、存在しなければならない。/ AllergyIntolerance.clinicalStatus SHALL be present if verificationStatus is not entered-in-error. / AllergyIntolerance.clinicalStatus SHALL be present if verificationStatus is not entered-in-error. {(verificationStatus.exists() and verificationStatus.coding.where(system='http://terminology.hl7.org/CodeSystem/allergyintolerance-verification' and code='entered-in-error').exists().not()) implies clinicalStatus.exists()}
+ait-2:AllergyIntolerance.verificationStatusに'entered-in-error'が入力されている場合、AllergyIntolerance.ClinicalStatusは、存在してはならない。 / AllergyIntolerance.clinicalStatus SHALL NOT be present if verification Status is entered-in-error {(verificationStatus.coding.where(system='http://terminology.hl7.org/CodeSystem/allergyintolerance-verification' and code='entered-in-error').exists()) implies clinicalStatus.exists().not()}dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照しなければならない。 / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where(((id.exists() and ('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url)))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(uri) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはあってはならない。 / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が存在することが望ましい / A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>Observation[classCode=OBS, moodCode=EVN]</t>
@@ -296,13 +296,13 @@
 </t>
   </si>
   <si>
-    <t>Logical id of this artifact</t>
-  </si>
-  <si>
-    <t>The logical id of the resource, as used in the URL for the resource. Once assigned, this value never changes.</t>
-  </si>
-  <si>
-    <t>The only time that a resource does not have an id is when it is being submitted to the server using a create operation.</t>
+    <t>このアーティファクトの論理ID / Logical id of this artifact</t>
+  </si>
+  <si>
+    <t>リソースのURLで使用されるリソースの論理ID。割り当てられたら、この値は変更されません。 / The logical id of the resource, as used in the URL for the resource. Once assigned, this value never changes.</t>
+  </si>
+  <si>
+    <t>リソースにIDがないのは、IDが作成操作を使用してサーバーに送信されている場合です。 / The only time that a resource does not have an id is when it is being submitted to the server using a create operation.</t>
   </si>
   <si>
     <t>Resource.id</t>
@@ -315,16 +315,16 @@
 </t>
   </si>
   <si>
-    <t>Metadata about the resource</t>
-  </si>
-  <si>
-    <t>The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
+    <t>リソースに関するMetadata / Metadata about the resource</t>
+  </si>
+  <si>
+    <t>リソースに関するMetadata。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
   </si>
   <si>
     <t>Resource.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
@@ -335,13 +335,13 @@
 </t>
   </si>
   <si>
-    <t>A set of rules under which this content was created</t>
-  </si>
-  <si>
-    <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
-  </si>
-  <si>
-    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
+    <t>このコンテンツが作成されたルールのセット / A set of rules under which this content was created</t>
+  </si>
+  <si>
+    <t>リソースが構築されたときに従った一連のルールへの参照。コンテンツの処理時に理解する必要があります。多くの場合、これは他のプロファイルなどとともに特別なルールを定義する実装ガイドへの参照です。 / A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
+  </si>
+  <si>
+    <t>このルールセットを主張することは、コンテンツが限られた取引パートナーのセットによってのみ理解されることを制限します。これにより、本質的に長期的にデータの有用性が制限されます。ただし、既存の健康エコシステムは非常に破壊されており、一般的に計算可能な意味でデータを定義、収集、交換する準備ができていません。可能な限り、実装者や仕様ライターはこの要素の使用を避ける必要があります。多くの場合、使用する場合、URLは、これらの特別なルールを他のプロファイル、バリューセットなどとともに叙述(Narative)の一部として定義する実装ガイドへの参照です。 / Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
   </si>
   <si>
     <t>Resource.implicitRules</t>
@@ -354,19 +354,19 @@
 </t>
   </si>
   <si>
-    <t>Language of the resource content</t>
-  </si>
-  <si>
-    <t>The base language in which the resource is written.</t>
-  </si>
-  <si>
-    <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
+    <t>リソースコンテンツの言語 / Language of the resource content</t>
+  </si>
+  <si>
+    <t>リソースが書かれている基本言語。 / The base language in which the resource is written.</t>
+  </si>
+  <si>
+    <t>言語は、インデックス作成とアクセシビリティをサポートするために提供されます（通常、テキストから音声までのサービスなどのサービスが言語タグを使用します）。叙述(Narative)のHTML言語タグは、叙述(Narative)に適用されます。リソース上の言語タグを使用して、リソース内のデータから生成された他のプレゼンテーションの言語を指定できます。すべてのコンテンツが基本言語である必要はありません。リソース。言語は、叙述(Narative)に自動的に適用されると想定されるべきではありません。言語が指定されている場合、HTMLのDIV要素にも指定されている場合（XML：LangとHTML Lang属性の関係については、HTML5のルールを参照してください）。 / Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
   </si>
   <si>
     <t>preferred</t>
   </si>
   <si>
-    <t>IETF language tag</t>
+    <t>IETF言語タグ / IETF language tag</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/languages|4.3.0</t>
@@ -389,10 +389,10 @@
     <t>Text summary of the resource, for human interpretation. このリソースを人間が解釈するためのテキスト要約</t>
   </si>
   <si>
-    <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
-  </si>
-  <si>
-    <t>Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
+    <t>リソースの概要を含み、人間へのリソースの内容を表すために使用できる人間の読み取り可能な叙述(Narative)。叙述(Narative)はすべての構造化されたデータをエンコードする必要はありませんが、人間が叙述(Narative)を読むだけで「臨床的に安全」にするために十分な詳細を含める必要があります。リソースの定義は、臨床的安全を確保するために、叙述(Narative)で表現するコンテンツを定義する場合があります。 / A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
+  </si>
+  <si>
+    <t>含まれるリソースには叙述(Narative)がありません。含まれていないリソースには叙述(Narative)が必要です。場合によっては、リソースには、追加の個別のデータがほとんどまたはまったくないテキストのみがあります（すべてのMinoccur = 1要素が満たされている限り）。これは、情報がtext blob (バイナリー ラージ オブジェクト)としてキャプチャされるレガシーシステムからのデータ、またはテキストが生またはナレーションされ、エンコードされた情報が後で追加される場合に必要になる場合があります。 / Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
   </si>
   <si>
     <t>DomainResource.text</t>
@@ -412,19 +412,19 @@
 </t>
   </si>
   <si>
-    <t>Contained, inline Resources</t>
-  </si>
-  <si>
-    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
-  </si>
-  <si>
-    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
+    <t>インラインリソースが含まれています / Contained, inline Resources</t>
+  </si>
+  <si>
+    <t>これらのリソースには、それらを含むリソースを除いて独立した存在はありません - 独立して特定することはできず、独自の独立したトランザクションスコープを持つこともできません。 / These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
+  </si>
+  <si>
+    <t>識別が失われると、コンテンツを適切に識別できる場合は、これを行うべきではありません。含まれるリソースには、メタ要素にプロファイルとタグがある場合がありますが、セキュリティラベルはありません。 / This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
   </si>
   <si>
     <t>DomainResource.contained</t>
   </si>
   <si>
-    <t xml:space="preserve">dom-r4b:Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
+    <t xml:space="preserve">dom-r4b:R4リソース内に新しいR4Bリソースを含めると、インスタンスがR4システムと共有された場合に相互運用性の問題が発生する可能性があります / Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
 </t>
   </si>
   <si>
@@ -442,33 +442,34 @@
 </t>
   </si>
   <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+    <t>実装で定義された追加のコンテンツ / Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>リソースの基本的な定義の一部ではない追加情報を表すために使用できます。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たされる一連の要件があります。 / May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>拡張機能を使用または定義する機関や管轄権に関係なく、アプリケーション、プロジェクト、または標準による拡張機能の使用に関連するスティグマはありません。拡張機能の使用は、FHIR仕様がすべての人にコアレベルのシンプルさを保持できるようにするものです。 / There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
     <t>DomainResource.extension</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>AllergyIntolerance.modifierExtension</t>
   </si>
   <si>
-    <t>Extensions that cannot be ignored</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+    <t>無視できない拡張機能 / Extensions that cannot be ignored</t>
+  </si>
+  <si>
+    <t>リソースの基本的な定義の一部ではなく、それを含む要素の理解および/または含有要素の子孫の理解を変更するために使用される場合があります。通常、修飾子要素は否定または資格を提供します。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義することが許可されていますが、拡張機能の定義の一部として満たされる一連の要件があります。アプリケーションの処理リソースは、修飾子拡張機能をチェックする必要があります。
+モディファイア拡張は、リソースまたはdomainResource上の要素の意味を変更してはなりません（修飾軸自体の意味を変更することはできません）。 / May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
+    <t>修飾子拡張機能により、安全に無視できる大部分の拡張機能と明確に区別できるように、安全に無視できない拡張機能が可能になります。これにより、実装者が拡張の存在を禁止する必要性を排除することにより、相互運用性が促進されます。詳細については、[修飾子拡張の定義]（拡張性.html＃modifierextension）を参照してください。 / Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
@@ -481,16 +482,16 @@
 </t>
   </si>
   <si>
-    <t>External ids for this item</t>
-  </si>
-  <si>
-    <t>Business identifiers assigned to this AllergyIntolerance by the performer or other systems which remain constant as the resource is updated and propagates from server to server.</t>
-  </si>
-  <si>
-    <t>This is a business identifier, not a resource identifier (see [discussion](http://hl7.org/fhir/R4B/resource.html#identifiers)).  It is best practice for the identifier to only appear on a single resource instance, however business practices may occasionally dictate that multiple resource instances with the same identifier can exist - possibly even with different resource types.  For example, multiple Patient and a Person resource instance might share the same social insurance number.</t>
-  </si>
-  <si>
-    <t>Allows identification of the AllergyIntolerance as it is known by various participating systems and in a way that remains consistent across servers.</t>
+    <t>このアイテムの外部ID / External ids for this item</t>
+  </si>
+  <si>
+    <t>リソースが更新され、サーバーからサーバーに伝播するにつれて一定のままであるパフォーマーまたは他のシステムによってこのアレルギー耐性に割り当てられたビジネスidentifier。 / Business identifiers assigned to this AllergyIntolerance by the performer or other systems which remain constant as the resource is updated and propagates from server to server.</t>
+  </si>
+  <si>
+    <t>これはビジネスidentifierであり、リソースidentifierではありません（[ディスカッション]（Resource.html＃identifierを参照））。identifierが単一のリソースインスタンスにのみ表示することがベストプラクティスですが、ビジネス慣行は、同じidentifierを持つ複数のリソースインスタンスが存在する可能性があることを時々決定する場合があります。たとえば、複数の患者と個人のリソースインスタンスは、同じ社会保険番号を共有する場合があります。 / This is a business identifier, not a resource identifier (see [discussion](http://hl7.org/fhir/R4B/resource.html#identifiers)).  It is best practice for the identifier to only appear on a single resource instance, however business practices may occasionally dictate that multiple resource instances with the same identifier can exist - possibly even with different resource types.  For example, multiple Patient and a Person resource instance might share the same social insurance number.</t>
+  </si>
+  <si>
+    <t>さまざまな参加システムで知られており、サーバー全体で一貫している方法でアレルギー耐性を識別できるようにします。 / Allows identification of the AllergyIntolerance as it is known by various participating systems and in a way that remains consistent across servers.</t>
   </si>
   <si>
     <t>id</t>
@@ -516,14 +517,15 @@
 このアレルギー不耐症のステータス。</t>
   </si>
   <si>
-    <t>Refer to [discussion](http://hl7.org/fhir/R4B/extensibility.html#Special-Case) if clincalStatus is missing data.
+    <t>Clincalstatusのデータが欠落している場合は、[Discussion]（Extensibility.html＃Special-Case）を参照してください。
+ClinicalStatusには臨床的判断が関与しているため、データ型はCodeAbleconceptです。そのため、必要なFHIR値セットが許可するよりも特異性が必要になる場合があります。たとえば、スノムコーディングにより、追加の特異性が可能になる場合があります。 / Refer to [discussion](http://hl7.org/fhir/R4B/extensibility.html#Special-Case) if clincalStatus is missing data.
 The data type is CodeableConcept because clinicalStatus has some clinical judgment involved, such that there might need to be more specificity than the required FHIR value set allows. For example, a SNOMED coding might allow for additional specificity.</t>
   </si>
   <si>
     <t>required</t>
   </si>
   <si>
-    <t>The clinical status of the allergy or intolerance.</t>
+    <t>アレルギーまたは不耐性の臨床状態。 / The clinical status of the allergy or intolerance.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/allergyintolerance-clinical|4.3.0</t>
@@ -549,10 +551,10 @@
 特定された物質（医薬品を含む）が有害反応を誘発する確実性の度合い。</t>
   </si>
   <si>
-    <t>The data type is CodeableConcept because verificationStatus has some clinical judgment involved, such that there might need to be more specificity than the required FHIR value set allows. For example, a SNOMED coding might allow for additional specificity.</t>
-  </si>
-  <si>
-    <t>Assertion about certainty associated with a propensity, or potential risk, of a reaction to the identified substance.</t>
+    <t>検証型には臨床的判断が含まれているため、データ型はCodeAbleconceptです。そのため、必要なFHIR値セットが許可するよりも特異性が必要になる場合があります。たとえば、スノムコーディングにより、追加の特異性が可能になる場合があります。 / The data type is CodeableConcept because verificationStatus has some clinical judgment involved, such that there might need to be more specificity than the required FHIR value set allows. For example, a SNOMED coding might allow for additional specificity.</t>
+  </si>
+  <si>
+    <t>特定された物質に対する反応の傾向または潜在的なリスクに関連する確実性に関する主張。 / Assertion about certainty associated with a propensity, or potential risk, of a reaction to the identified substance.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/allergyintolerance-verification|4.3.0</t>
@@ -575,10 +577,10 @@
 有害反応を誘発する生理的なメカニズムが特定できる場合にアレルギーか不耐性かを区別する。</t>
   </si>
   <si>
-    <t>Allergic (typically immune-mediated) reactions have been traditionally regarded as an indicator for potential escalation to significant future risk. Contemporary knowledge suggests that some reactions previously thought to be immune-mediated are, in fact, non-immune, but in some cases can still pose a life threatening risk. It is acknowledged that many clinicians might not be in a position to distinguish the mechanism of a particular reaction. Often the term "allergy" is used rather generically and may overlap with the use of "intolerance" - in practice the boundaries between these two concepts might not be well-defined or understood. This data element is included nevertheless, because many legacy systems have captured this attribute. Immunologic testing may provide supporting evidence for the basis of the reaction and the causative substance, but no tests are 100% sensitive or specific for sensitivity to a particular substance. If, as is commonly the case, it is unclear whether the reaction is due to an allergy or an intolerance, then the type element should be omitted from the resource.</t>
-  </si>
-  <si>
-    <t>Identification of the underlying physiological mechanism for a Reaction Risk.</t>
+    <t>アレルギー性（通常は免疫媒介）反応は、伝統的に、重大な将来のリスクへの潜在的なエスカレーションの指標と見なされてきました。現代の知識は、以前は免疫媒介であると考えられていたいくつかの反応は、実際には非免疫であるが、場合によっては生命を脅かすリスクをもたらす可能性があることを示唆しています。多くの臨床医が特定の反応のメカニズムを区別する立場にない可能性があることが認められています。多くの場合、「アレルギー」という用語はかなり一般的に使用され、「不寛容」の使用と重複する場合があります。実際には、これら2つの概念の境界は明確に定義されたり理解されたりしない場合があります。それでも、多くのレガシーシステムがこの属性をキャプチャしているため、このデータ要素が含まれています。免疫学的検査は、反応と原因物質の基礎についての支持的な証拠を提供する可能性がありますが、特定の物質に対する感受性に対して100％感度または特異的である検査はありません。一般的にそうであるように、反応がアレルギーまたは不耐性によるものであるかどうかが不明である場合、タイプ要素はリソースから省略する必要があります。 / Allergic (typically immune-mediated) reactions have been traditionally regarded as an indicator for potential escalation to significant future risk. Contemporary knowledge suggests that some reactions previously thought to be immune-mediated are, in fact, non-immune, but in some cases can still pose a life threatening risk. It is acknowledged that many clinicians might not be in a position to distinguish the mechanism of a particular reaction. Often the term "allergy" is used rather generically and may overlap with the use of "intolerance" - in practice the boundaries between these two concepts might not be well-defined or understood. This data element is included nevertheless, because many legacy systems have captured this attribute. Immunologic testing may provide supporting evidence for the basis of the reaction and the causative substance, but no tests are 100% sensitive or specific for sensitivity to a particular substance. If, as is commonly the case, it is unclear whether the reaction is due to an allergy or an intolerance, then the type element should be omitted from the resource.</t>
+  </si>
+  <si>
+    <t>反応リスクの基礎となる生理学的メカニズムの特定。 / Identification of the underlying physiological mechanism for a Reaction Risk.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/allergy-intolerance-type|4.3.0</t>
@@ -607,10 +609,10 @@
 同定された物質のカテゴリー。</t>
   </si>
   <si>
-    <t>This data element has been included because it is currently being captured in some clinical systems. This data can be derived from the substance where coding systems are used, and is effectively redundant in that situation.  When searching on category, consider the implications of AllergyIntolerance resources without a category.  For example, when searching on category = medication, medication allergies that don't have a category valued will not be returned.  Refer to [search](http://hl7.org/fhir/R4B/search.html) for more information on how to search category with a :missing modifier to get allergies that don't have a category.  Additionally, category should be used with caution because category can be subjective based on the sender.</t>
-  </si>
-  <si>
-    <t>Category of an identified substance associated with allergies or intolerances.</t>
+    <t>このデータ要素は、現在いくつかの臨床システムでキャプチャされているため、含まれています。このデータは、コーディングシステムが使用されている物質から導き出すことができ、その状況では効果的に冗長です。カテゴリを検索するときは、カテゴリなしでアレルギー耐性リソースの意味を考慮してください。たとえば、カテゴリ=薬で検索すると、評価されていないカテゴリがない薬物療法は返されません。[検索]（Search.html）を参照してください。カテゴリを失ったカテゴリを使用してカテゴリを検索する方法の詳細については、カテゴリを持たないアレルギーを取得します。さらに、カテゴリは送信者に基づいて主観的である可能性があるため、カテゴリは注意して使用する必要があります。 / This data element has been included because it is currently being captured in some clinical systems. This data can be derived from the substance where coding systems are used, and is effectively redundant in that situation.  When searching on category, consider the implications of AllergyIntolerance resources without a category.  For example, when searching on category = medication, medication allergies that don't have a category valued will not be returned.  Refer to [search](http://hl7.org/fhir/R4B/search.html) for more information on how to search category with a :missing modifier to get allergies that don't have a category.  Additionally, category should be used with caution because category can be subjective based on the sender.</t>
+  </si>
+  <si>
+    <t>アレルギーまたは不耐性に関連する同定された物質のカテゴリ。 / Category of an identified substance associated with allergies or intolerances.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/allergy-intolerance-category|4.3.0</t>
@@ -636,10 +638,10 @@
 同定された物質が誘発する有害反応の臨床的な重要度。</t>
   </si>
   <si>
-    <t>The default criticality value for any propensity to an adverse reaction should be 'Low Risk', indicating at the very least a relative contraindication to deliberate or voluntary exposure to the substance. 'High Risk' is flagged if the clinician has identified a propensity for a more serious or potentially life-threatening reaction, such as anaphylaxis, and implies an absolute contraindication to deliberate or voluntary exposure to the substance. If this element is missing, the criticality is unknown (though it may be known elsewhere).  Systems that capture a severity at the condition level are actually representing the concept of criticality whereas the severity documented at the reaction level is representing the true reaction severity.  Existing systems that are capturing both condition criticality and reaction severity may use the term "severity" to represent both.  Criticality is the worst it could be in the future (i.e. situation-agnostic) whereas severity is situation-dependent.</t>
-  </si>
-  <si>
-    <t>Estimate of the potential clinical harm, or seriousness, of a reaction to an identified substance.</t>
+    <t>副作用に対するあらゆる傾向のデフォルトのクリティカリティ値は「低リスク」である必要があり、少なくとも物質への意図的または自発的な暴露に対する相対的な禁忌を示しています。臨床医がアナフィラキシーなどのより深刻または潜在的に生命を脅かす反応の傾向を特定し、物質への意図的または自発的な暴露に対する絶対的な禁忌を暗示している場合、「高リスク」にフラグが立てられます。この要素が欠落している場合、臨界性は不明です（ただし、他の場所で知られている場合があります）。条件レベルで重症度をキャプチャするシステムは、実際には臨界の概念を表していますが、反応レベルで文書化された重大度は真の反応の重症度を表しています。条件の臨界性と反応の重症度の両方をキャプチャしている既存のシステムは、「重大度」という用語を使用して両方を表す場合があります。臨界性は、将来的には最悪です（つまり、状況に依存しない）が、重大度は状況に依存します。 / The default criticality value for any propensity to an adverse reaction should be 'Low Risk', indicating at the very least a relative contraindication to deliberate or voluntary exposure to the substance. 'High Risk' is flagged if the clinician has identified a propensity for a more serious or potentially life-threatening reaction, such as anaphylaxis, and implies an absolute contraindication to deliberate or voluntary exposure to the substance. If this element is missing, the criticality is unknown (though it may be known elsewhere).  Systems that capture a severity at the condition level are actually representing the concept of criticality whereas the severity documented at the reaction level is representing the true reaction severity.  Existing systems that are capturing both condition criticality and reaction severity may use the term "severity" to represent both.  Criticality is the worst it could be in the future (i.e. situation-agnostic) whereas severity is situation-dependent.</t>
+  </si>
+  <si>
+    <t>特定された物質に対する反応の潜在的な臨床的危害または深刻さの推定。 / Estimate of the potential clinical harm, or seriousness, of a reaction to an identified substance.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/allergy-intolerance-criticality|4.3.0</t>
@@ -830,7 +832,7 @@
 このアレルギー不耐症に関する情報の発生源または取得元。</t>
   </si>
   <si>
-    <t>The recorder takes responsibility for the content, but can reference the source from where they got it.</t>
+    <t>レコーダーはコンテンツに対して責任を負いますが、入手した場所からソースを参照できます。 / The recorder takes responsibility for the content, but can reference the source from where they got it.</t>
   </si>
   <si>
     <t>.participation[typeCode=INF].role</t>
@@ -852,7 +854,7 @@
 最も直近に発生した日時を表す。</t>
   </si>
   <si>
-    <t>This date may be replicated by one of the Onset of Reaction dates. Where a textual representation of the date of last occurrence is required e.g. 'In Childhood, '10 years ago' the Comment element should be used.</t>
+    <t>この日付は、反応日の開始の1つによって複製される場合があります。最後の発生の日付のテキスト表現が必要な場合。「10年前の幼少期に」コメント要素を使用する必要があります。 / This date may be replicated by one of the Onset of Reaction dates. Where a textual representation of the date of last occurrence is required e.g. 'In Childhood, '10 years ago' the Comment element should be used.</t>
   </si>
   <si>
     <t>outBoundRelationship[typeCode=SUBJ].target[classCode=OBS, moodCode=EVN, code &lt;= CommonClinicalObservationType, value &lt;= ObservationValue (Reaction Type)].effectiveTime</t>
@@ -872,7 +874,7 @@
 他のフィールド要素では表現できない、このアレルギー不耐症に関する追加的な記述。</t>
   </si>
   <si>
-    <t>For example: including reason for flagging a seriousness of 'High Risk'; and instructions related to future exposure or administration of the substance, such as administration within an Intensive Care Unit or under corticosteroid cover. The notes should be related to an allergy or intolerance as a condition in general and not related to any particular episode of it. For episode notes and descriptions, use AllergyIntolerance.event.description and  AllergyIntolerance.event.notes.</t>
+    <t>例：「高リスク」の深刻さにフラグを立てる理由を含む。集中治療室内またはコルチコステロイドカバーの下での投与など、将来の曝露または物質の投与に関連する指示。メモは、一般的な条件としてのアレルギーまたは不耐性に関連しており、その特定のエピソードとは関係ありません。エピソードノートと説明には、allergyIntolerance.event.descriptionとallergyIntolerance.event.notesを使用します。 / For example: including reason for flagging a seriousness of 'High Risk'; and instructions related to future exposure or administration of the substance, such as administration within an Intensive Care Unit or under corticosteroid cover. The notes should be related to an allergy or intolerance as a condition in general and not related to any particular episode of it. For episode notes and descriptions, use AllergyIntolerance.event.description and  AllergyIntolerance.event.notes.</t>
   </si>
   <si>
     <t>subjectOf.observationEvent[code="annotation"].value</t>
@@ -892,7 +894,7 @@
 同定された物質への暴露に関連する個々の有害反応に関する詳細情報。</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
+    <t xml:space="preserve">ele-1:空のParametersリソースでない限り、すべてのFHIR要素には@valueまたはchildrenが必要です / All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
 </t>
   </si>
   <si>
@@ -906,10 +908,10 @@
 </t>
   </si>
   <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+    <t>要素間参照のための一意のID / Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>リソース内の要素の一意のID（内部参照用）。これは、スペースを含まない文字列値である場合があります。 / Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
   </si>
   <si>
     <t>Element.id</t>
@@ -921,7 +923,7 @@
     <t>AllergyIntolerance.reaction.extension</t>
   </si>
   <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+    <t>要素の基本的な定義の一部ではない追加情報を表すために使用できます。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たされる一連の要件があります。 / May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
     <t>Element.extension</t>
@@ -934,10 +936,11 @@
 user contentmodifiers</t>
   </si>
   <si>
-    <t>Extensions that cannot be ignored even if unrecognized</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+    <t>認識されていなくても無視できない拡張機能 / Extensions that cannot be ignored even if unrecognized</t>
+  </si>
+  <si>
+    <t>要素の基本的な定義の一部ではなく、それが含まれている要素の理解、および/または含まれる要素の子孫の理解を変更するために使用される場合があります。通常、修飾子要素は否定または資格を提供します。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たされる一連の要件があります。アプリケーションの処理リソースは、修飾子拡張機能をチェックする必要があります。
+モディファイア拡張は、リソースまたはdomainResource上の要素の意味を変更してはなりません（修飾軸自体の意味を変更することはできません）。 / May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
@@ -957,10 +960,10 @@
 受信システムがAllergyIntolerance.reaction.substanceがAllergyIntolerance.codeのセマンティックスコープ内に（前者が後者の意味的な下位概念にあること）を確認できない場合、受信システムはAllergyIntolerance.reaction.substanceを無視する必要がある。</t>
   </si>
   <si>
-    <t>Coding of the specific substance (or pharmaceutical product) with a terminology capable of triggering decision support should be used wherever possible.  The 'code' element allows for the use of a specific substance or pharmaceutical product, or a group or class of substances. In the case of an allergy or intolerance to a class of substances, (for example, "penicillins"), the 'reaction.substance' element could be used to code the specific substance that was identified as having caused the reaction (for example, "amoxycillin"). Duplication of the value in the 'code' and 'reaction.substance' elements is acceptable when a specific substance has been recorded in 'code'.</t>
-  </si>
-  <si>
-    <t>Codes defining the type of the substance (including pharmaceutical products).</t>
+    <t>特定の物質（または医薬品）のコード化は、可能な限り、意思決定サポートをトリガーできる用語で使用する必要があります。「コード」要素は、特定の物質または医薬品、またはグループまたはクラスの物質を使用できるようにします。物質のクラスに対するアレルギーまたは不耐性の場合（たとえば、「ペニシリン」）、「反応」要素を使用して、反応を引き起こしたと特定された特定の物質をコーディングすることができます（たとえば、例えば、「アモキシシリン」）。「コード」と「反応」要素の値の複製は、特定の物質が「コード」に記録されている場合に受け入れられます。 / Coding of the specific substance (or pharmaceutical product) with a terminology capable of triggering decision support should be used wherever possible.  The 'code' element allows for the use of a specific substance or pharmaceutical product, or a group or class of substances. In the case of an allergy or intolerance to a class of substances, (for example, "penicillins"), the 'reaction.substance' element could be used to code the specific substance that was identified as having caused the reaction (for example, "amoxycillin"). Duplication of the value in the 'code' and 'reaction.substance' elements is acceptable when a specific substance has been recorded in 'code'.</t>
+  </si>
+  <si>
+    <t>物質のタイプを定義するコード（医薬品を含む）。 / Codes defining the type of the substance (including pharmaceutical products).</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/substance-code|4.3.0</t>
@@ -983,10 +986,10 @@
 この有害反応に関連する症状や兆候。</t>
   </si>
   <si>
-    <t>Manifestation can be expressed as a single word, phrase or brief description. For example: nausea, rash or no reaction. It is preferable that manifestation should be coded with a terminology, where possible. The values entered here may be used to display on an application screen as part of a list of adverse reactions, as recommended in the UK NHS CUI guidelines.  Terminologies commonly used include, but are not limited to, SNOMED CT or ICD10.</t>
-  </si>
-  <si>
-    <t>Clinical symptoms and/or signs that are observed or associated with an Adverse Reaction Event.</t>
+    <t>顕現は、単語、フレーズ、または簡単な説明として表現できます。例：吐き気、発疹、または反応なし。可能であれば、症状は用語でコード化することが望ましい。ここに入力された値は、英国NHS CUIガイドラインで推奨されるように、副作用のリストの一部としてアプリケーション画面に表示するために使用できます。一般的に使用される用語には、Snomed CTまたはICD10が含まれますが、これらに限定されません。 / Manifestation can be expressed as a single word, phrase or brief description. For example: nausea, rash or no reaction. It is preferable that manifestation should be coded with a terminology, where possible. The values entered here may be used to display on an application screen as part of a list of adverse reactions, as recommended in the UK NHS CUI guidelines.  Terminologies commonly used include, but are not limited to, SNOMED CT or ICD10.</t>
+  </si>
+  <si>
+    <t>有害反応イベントに観察または関連する臨床症状および/または徴候。 / Clinical symptoms and/or signs that are observed or associated with an Adverse Reaction Event.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/clinical-findings|4.3.0</t>
@@ -1009,7 +1012,7 @@
 必要であれば症状兆候の詳細も含めた、有害反応全体に関するテキストによる記述。</t>
   </si>
   <si>
-    <t>Use the description to provide any details of a particular event of the occurred reaction such as circumstances, reaction specifics, what happened before/after. Information, related to the event, but not describing a particular care should be captured in the comment field. For example: at the age of four, the patient was given penicillin for strep throat and subsequently developed severe hives.</t>
+    <t>説明を使用して、状況、反応の詳細、前後に起こったことなど、発生した反応の特定のイベントの詳細を提供します。イベントに関連する情報ですが、特定のケアを説明しない情報は、コメントフィールドに把握する必要があります。たとえば、4歳で、患者に連鎖球菌のペニシリンを投与され、その後重度のじんましんを発症しました。 / Use the description to provide any details of a particular event of the occurred reaction such as circumstances, reaction specifics, what happened before/after. Information, related to the event, but not describing a particular care should be captured in the comment field. For example: at the age of four, the patient was given penicillin for strep throat and subsequently developed severe hives.</t>
   </si>
   <si>
     <t>text</t>
@@ -1038,10 +1041,10 @@
 有害反応の重症度の全体としての臨床的な評価で、潜在的には複数の異なる症状兆候を考慮して決める。</t>
   </si>
   <si>
-    <t>It is acknowledged that this assessment is very subjective. There may be some specific practice domains where objective scales have been applied. Objective scales can be included in this model as extensions.</t>
-  </si>
-  <si>
-    <t>Clinical assessment of the severity of a reaction event as a whole, potentially considering multiple different manifestations.</t>
+    <t>この評価は非常に主観的であることが認められています。客観的なスケールが適用されている特定の実践ドメインがある場合があります。このモデルには、拡張機能として目的スケールを含めることができます。 / It is acknowledged that this assessment is very subjective. There may be some specific practice domains where objective scales have been applied. Objective scales can be included in this model as extensions.</t>
+  </si>
+  <si>
+    <t>反応イベント全体の重症度の臨床評価は、潜在的に複数の異なる症状を考慮しています。 / Clinical assessment of the severity of a reaction event as a whole, potentially considering multiple different manifestations.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/reaction-event-severity|4.3.0</t>
@@ -1057,10 +1060,10 @@
 患者がどのような経路でこの物質に暴露したかの同定。</t>
   </si>
   <si>
-    <t>Coding of the route of exposure with a terminology should be used wherever possible.</t>
-  </si>
-  <si>
-    <t>A coded concept describing the route or physiological path of administration of a therapeutic agent into or onto the body of a subject.</t>
+    <t>可能な限り、用語による露出経路のコーディングは、可能な限り使用する必要があります。 / Coding of the route of exposure with a terminology should be used wherever possible.</t>
+  </si>
+  <si>
+    <t>被験者の体への、またはそれへの治療剤の投与の経路または生理学的経路を説明するコード化された概念。 / A coded concept describing the route or physiological path of administration of a therapeutic agent into or onto the body of a subject.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/route-codes|4.3.0</t>
@@ -1079,7 +1082,7 @@
 他のフィールド要素では記述できない、有害反応に関する追加テキスト。</t>
   </si>
   <si>
-    <t>Use this field to record information indirectly related to a particular event and not captured in the description. For example: Clinical records are no longer available, recorded based on information provided to the patient by her mother and her mother is deceased.</t>
+    <t>このフィールドを使用して、特定のイベントに間接的に関連する情報を記録し、説明に記載されていません。たとえば、臨床記録は利用できなくなり、母親と母親が患者に提供した情報に基づいて記録されています。 / Use this field to record information indirectly related to a particular event and not captured in the description. For example: Clinical records are no longer available, recorded based on information provided to the patient by her mother and her mother is deceased.</t>
   </si>
 </sst>
 </file>
@@ -1410,7 +1413,7 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="106.67578125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="153.4765625" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="50.62109375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
